--- a/deals/451-white-horse-pike-atco-nj/451 White Horse Pike - Acquisition Model.xlsx
+++ b/deals/451-white-horse-pike-atco-nj/451 White Horse Pike - Acquisition Model.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="709">
   <si>
     <t xml:space="preserve">451 WHITE HORSE PIKE, ATCO NJ  —  ACQUISITION RECOMMENDATION</t>
   </si>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">Outparcel ground rent — base</t>
   </si>
   <si>
-    <t xml:space="preserve">Entitled pad land value $500k-$800k at an 8-9% ground-lease yield</t>
+    <t xml:space="preserve">Benchmarked to the listing agent's own build-to-suit comps: 7 Brew $155,000/yr and Wendy's $157,659/yr. A ground lease (tenant builds) typically runs 40-55% of a BTS rent</t>
   </si>
   <si>
     <t xml:space="preserve">EV charging licence — base</t>
@@ -1264,7 +1264,7 @@
     <t xml:space="preserve">0.75-1.0 AC</t>
   </si>
   <si>
-    <t xml:space="preserve">Entitled pad land value of $500k-$800k capitalized at an 8-9% ground-lease yield. QSR, coffee, car wash or medical pad.</t>
+    <t xml:space="preserve">Benchmarked to the listing agent's own comps: 7 Brew pays $155,000/yr and Wendy's $157,659/yr on build-to-suit pads. A ground lease, where the tenant builds, runs ~40-55% of that. QSR, coffee, car wash or medical pad.</t>
   </si>
   <si>
     <t xml:space="preserve">EV fast-charging licence</t>
@@ -1732,6 +1732,147 @@
     <t xml:space="preserve">The floor our offer is built on. Range $20-$24/SF; base case $22</t>
   </si>
   <si>
+    <t xml:space="preserve">TIER 3  —  COMPARABLES SUPPLIED BY THE LISTING AGENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Useful?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it actually shows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Brew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1390 Blackwood-Clementon Rd, Clementon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build-to-suit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 510 SF coffee kiosk at an apparent $303.92/SF. Nobody rents a building at that rate - the rent is for the PAD and drive-thru lanes, not the hut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301 White Horse Pike, Chesilhurst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose-built store with fuel on a large pad; rent repays land AND construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wendy's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69 NJ-73, Voorhees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose-built drive-thru restaurant - same land-plus-building economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501 Delsea Dr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sewell - lease signed 5 Jul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A genuine letting, but a very small unit - small units always rent high per foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walgreens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">625 N Black Horse Pike, Blackwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit BTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose-built pharmacy for a national credit tenant on a long-standing rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avis Budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341 N White Horse Pike, Lawnside - signed 5 Jun 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE ONE GENUINELY USEFUL COMP: second-hand building, same road, closest size to ours, recently signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142 NJ-73, Voorhees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grocery big box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At $12.96/SF it shows the opposite end of the same size effect - big buildings rent low per foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADJUSTING THE TWO GENUINE LETTINGS TO OUR BUILDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjustment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avis, Lawnside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin drive-thru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avis signed Jun-2025; Berlin is an asking rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bigger building than the comp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ours is 4,400 SF; larger boxes rent lower per foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atco is softer than Lawnside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lawnside is denser and closer in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-15 yr lease vs a 3-yr deal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short leases carry a premium rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDICATED RENT FOR OUR BUILDING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two independent routes converging on ~$22 - the seller's own evidence confirms the market rent we used</t>
+  </si>
+  <si>
     <t xml:space="preserve">HOW WE GOT TO $22  —  the adjustment reasoning</t>
   </si>
   <si>
@@ -1868,9 +2009,6 @@
   </si>
   <si>
     <t xml:space="preserve">Subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjustment</t>
   </si>
   <si>
     <t xml:space="preserve">Corporate / MSO guarantees</t>
@@ -2420,7 +2558,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="144">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2947,6 +3085,22 @@
     </xf>
     <xf numFmtId="164" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -3805,7 +3959,7 @@
       </c>
       <c r="B45" s="8" t="n">
         <f aca="false">'Land Upside'!C15</f>
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -3820,7 +3974,7 @@
       </c>
       <c r="B46" s="8" t="n">
         <f aca="false">'Land Upside'!C16</f>
-        <v>660810.810810811</v>
+        <v>931081.081081081</v>
       </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -3835,7 +3989,7 @@
       </c>
       <c r="B47" s="12" t="n">
         <f aca="false">(Assumptions!$B$22+'Land Upside'!C15)/Assumptions!$B$15</f>
-        <v>0.188181818181818</v>
+        <v>0.210909090909091</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
@@ -5469,7 +5623,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -5903,117 +6057,452 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="105" t="s">
+    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="B24" s="106" t="s">
+      <c r="G24" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="C24" s="106"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="106"/>
-    </row>
-    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="105" t="s">
+      <c r="H24" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="B25" s="106" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
         <v>554</v>
       </c>
-      <c r="C25" s="106"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="105" t="s">
+      <c r="B25" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="B26" s="106" t="s">
+      <c r="C25" s="126" t="n">
+        <v>510</v>
+      </c>
+      <c r="D25" s="132" t="n">
+        <f aca="false">E25/C25</f>
+        <v>303.921568627451</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>155000</v>
+      </c>
+      <c r="F25" s="109" t="s">
         <v>556</v>
       </c>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="106"/>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="105" t="s">
+      <c r="G25" s="133" t="s">
         <v>557</v>
       </c>
-      <c r="B27" s="106" t="s">
+      <c r="H25" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="C27" s="106"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="106"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="106"/>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="105" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
         <v>559</v>
       </c>
-      <c r="B28" s="106" t="s">
+      <c r="B26" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="C28" s="106"/>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="106"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="106"/>
-    </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="105" t="s">
+      <c r="C26" s="126" t="n">
+        <v>5585</v>
+      </c>
+      <c r="D26" s="134" t="n">
+        <f aca="false">E26/C26</f>
+        <v>58.1915846016115</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>325000</v>
+      </c>
+      <c r="F26" s="109" t="s">
+        <v>556</v>
+      </c>
+      <c r="G26" s="133" t="s">
+        <v>557</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="B29" s="106" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
         <v>562</v>
       </c>
-      <c r="C29" s="106"/>
-      <c r="D29" s="106"/>
-      <c r="E29" s="106"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="106"/>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="48" t="s">
+      <c r="B27" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
+      <c r="C27" s="126" t="n">
+        <v>3321</v>
+      </c>
+      <c r="D27" s="134" t="n">
+        <f aca="false">E27/C27</f>
+        <v>47.4733514001807</v>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>157659</v>
+      </c>
+      <c r="F27" s="109" t="s">
+        <v>556</v>
+      </c>
+      <c r="G27" s="133" t="s">
+        <v>557</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="24" t="s">
+        <v>565</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="C28" s="126" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D28" s="134" t="n">
+        <f aca="false">E28/C28</f>
+        <v>39.3299344501093</v>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>54000</v>
+      </c>
+      <c r="F28" s="109" t="s">
+        <v>567</v>
+      </c>
+      <c r="G28" s="133" t="s">
+        <v>568</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="24" t="s">
+        <v>570</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="C29" s="126" t="n">
+        <v>14870</v>
+      </c>
+      <c r="D29" s="134" t="n">
+        <f aca="false">E29/C29</f>
+        <v>31.1918628110289</v>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>463823</v>
+      </c>
+      <c r="F29" s="109" t="s">
+        <v>572</v>
+      </c>
+      <c r="G29" s="133" t="s">
+        <v>557</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="88" t="s">
+        <v>574</v>
+      </c>
+      <c r="B30" s="93" t="s">
+        <v>575</v>
+      </c>
+      <c r="C30" s="130" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D30" s="111" t="n">
+        <f aca="false">E30/C30</f>
+        <v>27.96</v>
+      </c>
+      <c r="E30" s="91" t="n">
+        <v>92268</v>
+      </c>
+      <c r="F30" s="135" t="s">
+        <v>567</v>
+      </c>
+      <c r="G30" s="92" t="s">
+        <v>576</v>
+      </c>
+      <c r="H30" s="93" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="s">
+        <v>578</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="C31" s="126" t="n">
+        <v>19054</v>
+      </c>
+      <c r="D31" s="134" t="n">
+        <f aca="false">E31/C31</f>
+        <v>12.9605332213708</v>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>246950</v>
+      </c>
+      <c r="F31" s="109" t="s">
+        <v>580</v>
+      </c>
+      <c r="G31" s="133" t="s">
+        <v>557</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="B35" s="37" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="C35" s="37" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B36" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C36" s="41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="B37" s="41" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C37" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="B38" s="41" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C38" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="43" t="s">
+        <v>595</v>
+      </c>
+      <c r="B39" s="111" t="n">
+        <f aca="false">B35*B36*B37*B38</f>
+        <v>21.51522</v>
+      </c>
+      <c r="C39" s="111" t="n">
+        <f aca="false">C35*C36*C37*C38</f>
+        <v>21.944</v>
+      </c>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="47" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="105" t="s">
+        <v>598</v>
+      </c>
+      <c r="B42" s="106" t="s">
+        <v>599</v>
+      </c>
+      <c r="C42" s="106"/>
+      <c r="D42" s="106"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="106"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="105" t="s">
+        <v>600</v>
+      </c>
+      <c r="B43" s="106" t="s">
+        <v>601</v>
+      </c>
+      <c r="C43" s="106"/>
+      <c r="D43" s="106"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="106"/>
+      <c r="G43" s="106"/>
+      <c r="H43" s="106"/>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="105" t="s">
+        <v>602</v>
+      </c>
+      <c r="B44" s="106" t="s">
+        <v>603</v>
+      </c>
+      <c r="C44" s="106"/>
+      <c r="D44" s="106"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="106"/>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="105" t="s">
+        <v>604</v>
+      </c>
+      <c r="B45" s="106" t="s">
+        <v>605</v>
+      </c>
+      <c r="C45" s="106"/>
+      <c r="D45" s="106"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="106"/>
+      <c r="H45" s="106"/>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="105" t="s">
+        <v>606</v>
+      </c>
+      <c r="B46" s="106" t="s">
+        <v>607</v>
+      </c>
+      <c r="C46" s="106"/>
+      <c r="D46" s="106"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="106"/>
+      <c r="H46" s="106"/>
+    </row>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="105" t="s">
+        <v>608</v>
+      </c>
+      <c r="B47" s="106" t="s">
+        <v>609</v>
+      </c>
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="106"/>
+      <c r="G47" s="106"/>
+      <c r="H47" s="106"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="A49:H49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6042,7 +6531,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6051,7 +6540,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6063,21 +6552,21 @@
         <v>512</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>566</v>
+        <v>613</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>567</v>
+        <v>614</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>460</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>568</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>569</v>
+        <v>616</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>337</v>
@@ -6086,15 +6575,15 @@
         <v>0.068</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>570</v>
+        <v>617</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>571</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>337</v>
@@ -6103,15 +6592,15 @@
         <v>0.074</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>573</v>
+        <v>620</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>575</v>
+        <v>622</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>3100000</v>
@@ -6120,32 +6609,32 @@
         <v>0.0825</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>576</v>
+        <v>623</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="121" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
       <c r="B8" s="124" t="n">
         <v>1600000</v>
       </c>
-      <c r="C8" s="132" t="n">
+      <c r="C8" s="136" t="n">
         <v>0.0825</v>
       </c>
       <c r="D8" s="122" t="s">
-        <v>578</v>
-      </c>
-      <c r="E8" s="133" t="s">
-        <v>579</v>
+        <v>625</v>
+      </c>
+      <c r="E8" s="137" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>580</v>
+        <v>627</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>1025000</v>
@@ -6154,15 +6643,15 @@
         <v>0.0887</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="E9" s="134" t="s">
-        <v>582</v>
+        <v>628</v>
+      </c>
+      <c r="E9" s="138" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>583</v>
+        <v>630</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>337</v>
@@ -6171,15 +6660,15 @@
         <v>0.0925</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>585</v>
+        <v>632</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>337</v>
@@ -6188,15 +6677,15 @@
         <v>0.0935</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>574</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>587</v>
+        <v>634</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>337</v>
@@ -6205,15 +6694,15 @@
         <v>0.0875</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>588</v>
+        <v>635</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>571</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="B13" s="52" t="n">
         <f aca="false">Assumptions!$B$15</f>
@@ -6224,15 +6713,15 @@
         <v>0.12</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>590</v>
-      </c>
-      <c r="E13" s="135" t="s">
-        <v>591</v>
+        <v>637</v>
+      </c>
+      <c r="E13" s="139" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>592</v>
+        <v>639</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -6241,16 +6730,16 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>594</v>
+        <v>641</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="E16" s="6"/>
     </row>
@@ -6259,43 +6748,43 @@
         <v>121</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>597</v>
+        <v>643</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>598</v>
+        <v>644</v>
       </c>
       <c r="D17" s="97" t="s">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="E17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>602</v>
+        <v>648</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
       <c r="E18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>604</v>
+        <v>650</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>606</v>
+        <v>652</v>
       </c>
       <c r="D19" s="97" t="s">
-        <v>603</v>
+        <v>649</v>
       </c>
       <c r="E19" s="10"/>
     </row>
@@ -6304,82 +6793,82 @@
         <v>131</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>607</v>
+        <v>653</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="D20" s="97" t="s">
-        <v>609</v>
+        <v>655</v>
       </c>
       <c r="E20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>610</v>
+        <v>656</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>611</v>
+        <v>657</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>612</v>
+        <v>658</v>
       </c>
       <c r="D21" s="97" t="s">
-        <v>613</v>
+        <v>659</v>
       </c>
       <c r="E21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>614</v>
+        <v>660</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>615</v>
+        <v>661</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>616</v>
+        <v>662</v>
       </c>
       <c r="D22" s="96" t="s">
-        <v>617</v>
+        <v>663</v>
       </c>
       <c r="E22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>618</v>
+        <v>664</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>615</v>
+        <v>661</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>619</v>
+        <v>665</v>
       </c>
       <c r="D23" s="96" t="s">
-        <v>620</v>
+        <v>666</v>
       </c>
       <c r="E23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43" t="s">
-        <v>621</v>
-      </c>
-      <c r="B24" s="136" t="s">
-        <v>622</v>
-      </c>
-      <c r="C24" s="136" t="s">
-        <v>623</v>
+        <v>667</v>
+      </c>
+      <c r="B24" s="140" t="s">
+        <v>668</v>
+      </c>
+      <c r="C24" s="140" t="s">
+        <v>669</v>
       </c>
       <c r="D24" s="62" t="n">
         <f aca="false">Assumptions!$B$22/Assumptions!$B$15</f>
         <v>0.12</v>
       </c>
-      <c r="E24" s="137" t="s">
-        <v>624</v>
+      <c r="E24" s="141" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>625</v>
+        <v>671</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -6418,194 +6907,194 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>672</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>627</v>
+        <v>673</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>628</v>
+        <v>674</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>629</v>
+        <v>675</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>630</v>
+        <v>676</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>631</v>
+        <v>677</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>632</v>
+        <v>678</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>633</v>
+        <v>679</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>634</v>
+        <v>680</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>635</v>
+        <v>681</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>636</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>637</v>
+        <v>683</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>638</v>
+        <v>684</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>639</v>
+        <v>685</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>640</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>641</v>
+        <v>687</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>642</v>
+        <v>688</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>643</v>
+        <v>689</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>644</v>
+        <v>690</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>645</v>
+        <v>691</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>646</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="138" t="s">
-        <v>648</v>
+      <c r="A16" s="142" t="s">
+        <v>694</v>
       </c>
       <c r="B16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="139" t="s">
-        <v>649</v>
-      </c>
-      <c r="B17" s="139"/>
+      <c r="A17" s="143" t="s">
+        <v>695</v>
+      </c>
+      <c r="B17" s="143"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="139" t="s">
-        <v>650</v>
-      </c>
-      <c r="B18" s="139"/>
+      <c r="A18" s="143" t="s">
+        <v>696</v>
+      </c>
+      <c r="B18" s="143"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139" t="s">
-        <v>651</v>
-      </c>
-      <c r="B19" s="139"/>
+      <c r="A19" s="143" t="s">
+        <v>697</v>
+      </c>
+      <c r="B19" s="143"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="139" t="s">
-        <v>652</v>
-      </c>
-      <c r="B20" s="139"/>
+      <c r="A20" s="143" t="s">
+        <v>698</v>
+      </c>
+      <c r="B20" s="143"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="139" t="s">
-        <v>653</v>
-      </c>
-      <c r="B21" s="139"/>
+      <c r="A21" s="143" t="s">
+        <v>699</v>
+      </c>
+      <c r="B21" s="143"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="139" t="s">
-        <v>654</v>
-      </c>
-      <c r="B22" s="139"/>
+      <c r="A22" s="143" t="s">
+        <v>700</v>
+      </c>
+      <c r="B22" s="143"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="138" t="s">
-        <v>655</v>
+      <c r="A24" s="142" t="s">
+        <v>701</v>
       </c>
       <c r="B24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="139" t="s">
-        <v>656</v>
-      </c>
-      <c r="B25" s="139"/>
+      <c r="A25" s="143" t="s">
+        <v>702</v>
+      </c>
+      <c r="B25" s="143"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="139" t="s">
-        <v>657</v>
-      </c>
-      <c r="B26" s="139"/>
+      <c r="A26" s="143" t="s">
+        <v>703</v>
+      </c>
+      <c r="B26" s="143"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="139" t="s">
-        <v>658</v>
-      </c>
-      <c r="B27" s="139"/>
+      <c r="A27" s="143" t="s">
+        <v>704</v>
+      </c>
+      <c r="B27" s="143"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="139" t="s">
-        <v>659</v>
-      </c>
-      <c r="B28" s="139"/>
+      <c r="A28" s="143" t="s">
+        <v>705</v>
+      </c>
+      <c r="B28" s="143"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="139" t="s">
-        <v>660</v>
-      </c>
-      <c r="B29" s="139"/>
+      <c r="A29" s="143" t="s">
+        <v>706</v>
+      </c>
+      <c r="B29" s="143"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="139" t="s">
-        <v>661</v>
-      </c>
-      <c r="B30" s="139"/>
+      <c r="A30" s="143" t="s">
+        <v>707</v>
+      </c>
+      <c r="B30" s="143"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="139" t="s">
-        <v>662</v>
-      </c>
-      <c r="B31" s="139"/>
+      <c r="A31" s="143" t="s">
+        <v>708</v>
+      </c>
+      <c r="B31" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -7112,12 +7601,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
         <v>157</v>
       </c>
       <c r="B44" s="34" t="n">
-        <v>55000</v>
+        <v>80000</v>
       </c>
       <c r="C44" s="31" t="s">
         <v>125</v>
@@ -11055,19 +11544,19 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
         <v>392</v>
       </c>
       <c r="B13" s="34" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="C13" s="42" t="n">
         <f aca="false">Assumptions!$B$44</f>
-        <v>55000</v>
+        <v>80000</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>75000</v>
+        <v>110000</v>
       </c>
       <c r="E13" s="109" t="s">
         <v>393</v>
@@ -11103,15 +11592,15 @@
       </c>
       <c r="B15" s="46" t="n">
         <f aca="false">SUM(B13:B14)</f>
-        <v>52000</v>
+        <v>72000</v>
       </c>
       <c r="C15" s="46" t="n">
         <f aca="false">SUM(C13:C14)</f>
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="D15" s="46" t="n">
         <f aca="false">SUM(D13:D14)</f>
-        <v>109000</v>
+        <v>144000</v>
       </c>
       <c r="E15" s="110" t="s">
         <v>399</v>
@@ -11126,15 +11615,15 @@
       </c>
       <c r="B16" s="8" t="n">
         <f aca="false">B15/Assumptions!$B$47-Assumptions!$B$46</f>
-        <v>412162.162162162</v>
+        <v>628378.378378378</v>
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">C15/Assumptions!$B$47-Assumptions!$B$46</f>
-        <v>660810.810810811</v>
+        <v>931081.081081081</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">D15/Assumptions!$B$47-Assumptions!$B$46</f>
-        <v>1028378.37837838</v>
+        <v>1406756.75675676</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="11" t="s">
@@ -11157,7 +11646,7 @@
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">Assumptions!$B$22+C15</f>
-        <v>207000</v>
+        <v>232000</v>
       </c>
       <c r="C19" s="53" t="s">
         <v>405</v>
@@ -11172,7 +11661,7 @@
       </c>
       <c r="B20" s="12" t="n">
         <f aca="false">(Assumptions!$B$22+C15)/Assumptions!$B$15</f>
-        <v>0.188181818181818</v>
+        <v>0.210909090909091</v>
       </c>
       <c r="C20" s="53" t="s">
         <v>407</v>
@@ -11202,7 +11691,7 @@
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">C16/Assumptions!$B$15</f>
-        <v>0.600737100737101</v>
+        <v>0.846437346437347</v>
       </c>
       <c r="C22" s="53" t="s">
         <v>411</v>
@@ -11217,7 +11706,7 @@
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">(18*Assumptions!$B$7+C15)/Assumptions!$B$15</f>
-        <v>0.140181818181818</v>
+        <v>0.162909090909091</v>
       </c>
       <c r="C23" s="53" t="s">
         <v>413</v>

--- a/deals/451-white-horse-pike-atco-nj/451 White Horse Pike - Acquisition Model.xlsx
+++ b/deals/451-white-horse-pike-atco-nj/451 White Horse Pike - Acquisition Model.xlsx
@@ -16,11 +16,12 @@
     <sheet name="Re-Rent Analysis" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Re-Leasing Options" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Land Upside" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Financing" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Stress Tests" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Lease Comps" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Sale Comps" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Risks &amp; Diligence" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Growth Plan" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Financing" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Stress Tests" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Lease Comps" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sale Comps" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Risks &amp; Diligence" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="764">
   <si>
     <t xml:space="preserve">451 WHITE HORSE PIKE, ATCO NJ  —  ACQUISITION RECOMMENDATION</t>
   </si>
@@ -1357,6 +1358,174 @@
     <t xml:space="preserve">Tesla historically pays site hosts little or no ground rent, and its newer Supercharger for Business program is host-owned, meaning we would fund the hardware. The rent is with third-party operators who fund 100% of capex.</t>
   </si>
   <si>
+    <t xml:space="preserve">GROWTH PLAN  —  the ten-year value-creation case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three cases over a 10-year hold. The land is EXCLUDED from the floor and base cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTIONS FOR THE GROWTH CASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-let rent to a medical covenant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/SF - see Re-Leasing Options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent increases on the new lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual - the flaw the current lease has</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fit-out contribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$60/SF medical fit-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letting fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5% of the first 10 years' rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit cap - growth case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A non-cannabis covenant is financeable, so tighter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit cap - base case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No land income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit cap - floor case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weak covenant, wide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor-case re-let rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/SF - bottom of the corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEN-YEAR CASH FLOW  —  GROWTH CASE (land executed, building re-let)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sale at year 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE THREE CASES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlevered IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What has to happen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor - nothing goes right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tenant fails, land never developed, building re-let at $18/SF and sold at a 9.00% cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base - the ordinary path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building re-let to a medical or bank covenant at $24/SF. Land left alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth - the plan works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land monetised AND building re-let on a 10-15 yr lease with increases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUE BRIDGE  —  where the value is created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What changed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where we start - buy at our offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannabis rent, 6.5 yrs left, no growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the spare land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building plot let, EV chargers licensed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-let the building on a proper lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical rent with increases replaces cannabis rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An ordinary tenant means it is mortgageable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wider buyer pool tightens the sale yield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less what it costs to get there</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land works, fit-out and letting fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STABILISED VALUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roughly double our entry price, over about ten years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain on our basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The land is excluded from the floor and base cases, and from every return elsewhere in this workbook. It is free option value - we should never bid the price up for it. Note also that leverage magnifies both directions: in the floor case a 55% mortgage turns +5.4% into roughly -3.7%.</t>
+  </si>
+  <si>
     <t xml:space="preserve">FINANCING  —  can he borrow against it, and what does leverage do?</t>
   </si>
   <si>
@@ -1433,9 +1602,6 @@
   </si>
   <si>
     <t xml:space="preserve">Levered IRR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unlevered IRR</t>
   </si>
   <si>
     <t xml:space="preserve">Leverage adds</t>
@@ -2558,7 +2724,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="147">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3000,6 +3166,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4118,6 +4296,565 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:S23"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="12" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="L4" s="51" t="n">
+        <f aca="false">-B18</f>
+        <v>-495000</v>
+      </c>
+      <c r="M4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="N4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="O4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="P4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="Q4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="R4" s="51" t="n">
+        <f aca="false">C18</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="S4" s="51" t="n">
+        <f aca="false">C18*0.5+E18</f>
+        <v>643328.111643992</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B5" s="38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="L5" s="51" t="n">
+        <f aca="false">-B19</f>
+        <v>-562500</v>
+      </c>
+      <c r="M5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="N5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="O5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="P5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="Q5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="R5" s="51" t="n">
+        <f aca="false">C19</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="S5" s="51" t="n">
+        <f aca="false">C19*0.5+E19</f>
+        <v>563122.791792153</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="B6" s="38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="L6" s="51" t="n">
+        <f aca="false">-B20</f>
+        <v>-720000</v>
+      </c>
+      <c r="M6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="N6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="O6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="P6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="Q6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="R6" s="51" t="n">
+        <f aca="false">C20</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="S6" s="51" t="n">
+        <f aca="false">C20*0.5+E20</f>
+        <v>375977.045471196</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B7" s="103" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>491</v>
+      </c>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <f aca="false">Assumptions!$B$15*$B$5</f>
+        <v>605000</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <f aca="false">Assumptions!$B$15-B12</f>
+        <v>495000</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <f aca="false">-PMT($B$6/12,$B$7*12,B12)*12</f>
+        <v>65971.6741262084</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>132000</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <f aca="false">E12/D12</f>
+        <v>2.00085872836082</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <f aca="false">E12-D12</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <f aca="false">G12/C12</f>
+        <v>0.133390557320791</v>
+      </c>
+      <c r="I12" s="11" t="str">
+        <f aca="false">IF(F12&gt;=1.5,"Comfortably financeable",IF(F12&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
+        <v>Comfortably financeable</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <f aca="false">Assumptions!$B$16*$B$5</f>
+        <v>687500</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <f aca="false">Assumptions!$B$16-B13</f>
+        <v>562500</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <f aca="false">-PMT($B$6/12,$B$7*12,B13)*12</f>
+        <v>74967.811507055</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>132000</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <f aca="false">E13/D13</f>
+        <v>1.76075568095752</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <f aca="false">E13-D13</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <f aca="false">G13/C13</f>
+        <v>0.101390557320791</v>
+      </c>
+      <c r="I13" s="11" t="str">
+        <f aca="false">IF(F13&gt;=1.5,"Comfortably financeable",IF(F13&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
+        <v>Comfortably financeable</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <f aca="false">Assumptions!$B$14*$B$5</f>
+        <v>880000</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <f aca="false">Assumptions!$B$14-B14</f>
+        <v>720000</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <f aca="false">-PMT($B$6/12,$B$7*12,B14)*12</f>
+        <v>95958.7987290304</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>132000</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <f aca="false">E14/D14</f>
+        <v>1.37559037574807</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <f aca="false">E14-D14</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <f aca="false">G14/C14</f>
+        <v>0.0500572239874578</v>
+      </c>
+      <c r="I14" s="11" t="str">
+        <f aca="false">IF(F14&gt;=1.5,"Comfortably financeable",IF(F14&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
+        <v>Financeable, tight</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="25" t="n">
+        <f aca="false">C12</f>
+        <v>495000</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <f aca="false">G12</f>
+        <v>66028.3258737916</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <f aca="false">B12*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B12))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
+        <v>555186.508517046</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <f aca="false">'Reversion Scenarios'!$G$11-D18</f>
+        <v>610313.948707096</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">IRR(L4:S4)</f>
+        <v>0.148484517194147</v>
+      </c>
+      <c r="G18" s="65" t="n">
+        <f aca="false">Returns!$D$31</f>
+        <v>0.119954981443023</v>
+      </c>
+      <c r="H18" s="65" t="n">
+        <f aca="false">F18-G18</f>
+        <v>0.0285295357511241</v>
+      </c>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="25" t="n">
+        <f aca="false">C13</f>
+        <v>562500</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <f aca="false">G13</f>
+        <v>57032.188492945</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <f aca="false">B13*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B13))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
+        <v>630893.759678461</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <f aca="false">'Reversion Scenarios'!$G$11-D19</f>
+        <v>534606.69754568</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">IRR(L5:S5)</f>
+        <v>0.09050766214664</v>
+      </c>
+      <c r="G19" s="65" t="n">
+        <f aca="false">Returns!$D$34</f>
+        <v>0.0926183792510331</v>
+      </c>
+      <c r="H19" s="65" t="n">
+        <f aca="false">F19-G19</f>
+        <v>-0.00211071710439302</v>
+      </c>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="25" t="n">
+        <f aca="false">C14</f>
+        <v>720000</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <f aca="false">G14</f>
+        <v>36041.2012709696</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <f aca="false">B14*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B14))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
+        <v>807544.01238843</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <f aca="false">'Reversion Scenarios'!$G$11-D20</f>
+        <v>357956.444835711</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <f aca="false">IRR(L6:S6)</f>
+        <v>-0.0332012262877994</v>
+      </c>
+      <c r="G20" s="65" t="n">
+        <f aca="false">Returns!$D$37</f>
+        <v>0.0432884758639595</v>
+      </c>
+      <c r="H20" s="65" t="n">
+        <f aca="false">F20-G20</f>
+        <v>-0.0764897021517589</v>
+      </c>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="48" t="s">
+        <v>508</v>
+      </c>
+      <c r="B22" s="48"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A22:I23"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:AI49"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4129,7 +4866,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4140,7 +4877,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>455</v>
+        <v>510</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4151,7 +4888,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>456</v>
+        <v>511</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4258,19 +4995,19 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="J5" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4371,7 +5108,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="B6" s="42" t="n">
         <f aca="false">Assumptions!$B$22</f>
@@ -4385,7 +5122,7 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11" t="s">
-        <v>462</v>
+        <v>517</v>
       </c>
       <c r="J6" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4500,7 +5237,7 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11" t="s">
-        <v>463</v>
+        <v>518</v>
       </c>
       <c r="J7" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4615,7 +5352,7 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11" t="s">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="J8" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4730,7 +5467,7 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11" t="s">
-        <v>465</v>
+        <v>520</v>
       </c>
       <c r="J9" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4831,13 +5568,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="B10" s="46" t="n">
         <f aca="false">SUM(B6:B9)</f>
         <v>193402</v>
       </c>
-      <c r="C10" s="111" t="n">
+      <c r="C10" s="114" t="n">
         <f aca="false">B10/Assumptions!$B$7</f>
         <v>43.955</v>
       </c>
@@ -4845,7 +5582,7 @@
       <c r="E10" s="45"/>
       <c r="F10" s="45"/>
       <c r="G10" s="47" t="s">
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="J10" s="51" t="n">
         <f aca="false">-Assumptions!$B$15</f>
@@ -4946,102 +5683,102 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>468</v>
+        <v>523</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>469</v>
+        <v>524</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>470</v>
+        <v>525</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>473</v>
+        <v>528</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>474</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="B13" s="112" t="n">
+        <v>530</v>
+      </c>
+      <c r="B13" s="115" t="n">
         <f aca="false">$B$10/1500000</f>
         <v>0.128934666666667</v>
       </c>
-      <c r="C13" s="112" t="n">
+      <c r="C13" s="115" t="n">
         <f aca="false">$B$10/2000000</f>
         <v>0.096701</v>
       </c>
-      <c r="D13" s="112" t="n">
+      <c r="D13" s="115" t="n">
         <f aca="false">$B$10/2500000</f>
         <v>0.0773608</v>
       </c>
-      <c r="E13" s="112" t="n">
+      <c r="E13" s="115" t="n">
         <f aca="false">$B$10/3000000</f>
         <v>0.0644673333333333</v>
       </c>
-      <c r="F13" s="112" t="n">
+      <c r="F13" s="115" t="n">
         <f aca="false">$B$10/3900000</f>
         <v>0.0495902564102564</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>476</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="B14" s="113" t="str">
+        <v>500</v>
+      </c>
+      <c r="B14" s="116" t="str">
         <f aca="false">IF(B13&gt;0.09,"Distressed",IF(B13&gt;0.07,"Tight",IF(B13&gt;0.055,"Workable","Healthy")))</f>
         <v>Distressed</v>
       </c>
-      <c r="C14" s="113" t="str">
+      <c r="C14" s="116" t="str">
         <f aca="false">IF(C13&gt;0.09,"Distressed",IF(C13&gt;0.07,"Tight",IF(C13&gt;0.055,"Workable","Healthy")))</f>
         <v>Distressed</v>
       </c>
-      <c r="D14" s="113" t="str">
+      <c r="D14" s="116" t="str">
         <f aca="false">IF(D13&gt;0.09,"Distressed",IF(D13&gt;0.07,"Tight",IF(D13&gt;0.055,"Workable","Healthy")))</f>
         <v>Tight</v>
       </c>
-      <c r="E14" s="113" t="str">
+      <c r="E14" s="116" t="str">
         <f aca="false">IF(E13&gt;0.09,"Distressed",IF(E13&gt;0.07,"Tight",IF(E13&gt;0.055,"Workable","Healthy")))</f>
         <v>Workable</v>
       </c>
-      <c r="F14" s="113" t="str">
+      <c r="F14" s="116" t="str">
         <f aca="false">IF(F13&gt;0.09,"Distressed",IF(F13&gt;0.07,"Tight",IF(F13&gt;0.055,"Workable","Healthy")))</f>
         <v>Healthy</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>477</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="B15" s="8" t="n">
         <f aca="false">$B$10/0.09</f>
         <v>2148911.11111111</v>
       </c>
-      <c r="C15" s="114" t="s">
-        <v>479</v>
-      </c>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="114"/>
+      <c r="C15" s="117" t="s">
+        <v>534</v>
+      </c>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>480</v>
+        <v>535</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5052,23 +5789,23 @@
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>481</v>
+        <v>536</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>482</v>
+        <v>537</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>228</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>483</v>
+        <v>538</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>229</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6" t="s">
-        <v>484</v>
+        <v>539</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5092,8 +5829,8 @@
         <v>0.0285408210943198</v>
       </c>
       <c r="F19" s="10"/>
-      <c r="G19" s="115" t="s">
-        <v>485</v>
+      <c r="G19" s="118" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5117,12 +5854,12 @@
         <v>0.0323630247287839</v>
       </c>
       <c r="F20" s="10"/>
-      <c r="G20" s="115" t="s">
-        <v>485</v>
+      <c r="G20" s="118" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="116" t="n">
+      <c r="A21" s="119" t="n">
         <v>0.4</v>
       </c>
       <c r="B21" s="91" t="n">
@@ -5143,7 +5880,7 @@
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="77" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5167,7 +5904,7 @@
         <v>0.0501656529790763</v>
       </c>
       <c r="F22" s="10"/>
-      <c r="G22" s="115"/>
+      <c r="G22" s="118"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="41" t="n">
@@ -5190,7 +5927,7 @@
         <v>0.0567531639585837</v>
       </c>
       <c r="F23" s="10"/>
-      <c r="G23" s="115"/>
+      <c r="G23" s="118"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="41" t="n">
@@ -5213,8 +5950,8 @@
         <v>0.0661465756202188</v>
       </c>
       <c r="F24" s="10"/>
-      <c r="G24" s="115" t="s">
-        <v>487</v>
+      <c r="G24" s="118" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5238,13 +5975,13 @@
         <v>0.0750183427903719</v>
       </c>
       <c r="F25" s="10"/>
-      <c r="G25" s="115" t="s">
-        <v>487</v>
+      <c r="G25" s="118" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>488</v>
+        <v>543</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -5264,7 +6001,7 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>489</v>
+        <v>544</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -5275,23 +6012,23 @@
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>490</v>
+        <v>545</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>440</v>
+        <v>496</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>491</v>
+        <v>546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6" t="s">
-        <v>484</v>
+        <v>539</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5310,13 +6047,13 @@
         <f aca="false">B31/0.0875</f>
         <v>804571.428571429</v>
       </c>
-      <c r="E31" s="117" t="n">
+      <c r="E31" s="120" t="n">
         <f aca="false">D31/Assumptions!$B$15-1</f>
         <v>-0.268571428571428</v>
       </c>
       <c r="F31" s="10"/>
-      <c r="G31" s="118" t="s">
-        <v>493</v>
+      <c r="G31" s="121" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5335,12 +6072,12 @@
         <f aca="false">B32/0.0875</f>
         <v>905142.857142857</v>
       </c>
-      <c r="E32" s="117" t="n">
+      <c r="E32" s="120" t="n">
         <f aca="false">D32/Assumptions!$B$15-1</f>
         <v>-0.177142857142857</v>
       </c>
       <c r="F32" s="10"/>
-      <c r="G32" s="118"/>
+      <c r="G32" s="121"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="37" t="n">
@@ -5358,15 +6095,15 @@
         <f aca="false">B33/0.0875</f>
         <v>1005714.28571429</v>
       </c>
-      <c r="E33" s="117" t="n">
+      <c r="E33" s="120" t="n">
         <f aca="false">D33/Assumptions!$B$15-1</f>
         <v>-0.0857142857142856</v>
       </c>
       <c r="F33" s="10"/>
-      <c r="G33" s="118"/>
+      <c r="G33" s="121"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="119" t="n">
+      <c r="A34" s="122" t="n">
         <v>22</v>
       </c>
       <c r="B34" s="91" t="n">
@@ -5381,13 +6118,13 @@
         <f aca="false">B34/0.0875</f>
         <v>1106285.71428571</v>
       </c>
-      <c r="E34" s="120" t="n">
+      <c r="E34" s="123" t="n">
         <f aca="false">D34/Assumptions!$B$15-1</f>
         <v>0.00571428571428578</v>
       </c>
       <c r="F34" s="45"/>
       <c r="G34" s="47" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5406,12 +6143,12 @@
         <f aca="false">B35/0.0875</f>
         <v>1206857.14285714</v>
       </c>
-      <c r="E35" s="117" t="n">
+      <c r="E35" s="120" t="n">
         <f aca="false">D35/Assumptions!$B$15-1</f>
         <v>0.0971428571428572</v>
       </c>
       <c r="F35" s="10"/>
-      <c r="G35" s="118"/>
+      <c r="G35" s="121"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="37" t="n">
@@ -5429,16 +6166,16 @@
         <f aca="false">B36/0.0875</f>
         <v>1307428.57142857</v>
       </c>
-      <c r="E36" s="117" t="n">
+      <c r="E36" s="120" t="n">
         <f aca="false">D36/Assumptions!$B$15-1</f>
         <v>0.188571428571429</v>
       </c>
       <c r="F36" s="10"/>
-      <c r="G36" s="118"/>
+      <c r="G36" s="121"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>495</v>
+        <v>550</v>
       </c>
       <c r="B37" s="48"/>
       <c r="C37" s="48"/>
@@ -5458,7 +6195,7 @@
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>496</v>
+        <v>551</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -5469,10 +6206,10 @@
     </row>
     <row r="41" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>497</v>
+        <v>552</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>498</v>
+        <v>553</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>175</v>
@@ -5483,12 +6220,12 @@
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6" t="s">
-        <v>499</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="20" t="s">
-        <v>500</v>
+        <v>555</v>
       </c>
       <c r="B42" s="25" t="n">
         <v>154000</v>
@@ -5503,12 +6240,12 @@
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="11" t="s">
-        <v>501</v>
+        <v>556</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>502</v>
+        <v>557</v>
       </c>
       <c r="B43" s="25" t="n">
         <v>105600</v>
@@ -5523,12 +6260,12 @@
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="11" t="s">
-        <v>503</v>
+        <v>558</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>504</v>
+        <v>559</v>
       </c>
       <c r="B44" s="25" t="n">
         <v>105600</v>
@@ -5543,12 +6280,12 @@
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="11" t="s">
-        <v>505</v>
+        <v>560</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="20" t="s">
-        <v>506</v>
+        <v>561</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>337</v>
@@ -5563,12 +6300,12 @@
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="11" t="s">
-        <v>507</v>
+        <v>562</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="48" t="s">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="B47" s="48"/>
       <c r="C47" s="48"/>
@@ -5618,7 +6355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -5638,7 +6375,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>509</v>
+        <v>564</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5650,7 +6387,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>510</v>
+        <v>565</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5662,7 +6399,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>511</v>
+        <v>566</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -5674,10 +6411,10 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>513</v>
+        <v>568</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>101</v>
@@ -5686,53 +6423,53 @@
         <v>316</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>515</v>
+        <v>570</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="121" t="s">
-        <v>517</v>
-      </c>
-      <c r="B6" s="122" t="s">
-        <v>518</v>
-      </c>
-      <c r="C6" s="123" t="n">
+      <c r="A6" s="124" t="s">
+        <v>572</v>
+      </c>
+      <c r="B6" s="125" t="s">
+        <v>573</v>
+      </c>
+      <c r="C6" s="126" t="n">
         <v>4400</v>
       </c>
       <c r="D6" s="98" t="n">
         <v>30</v>
       </c>
-      <c r="E6" s="124" t="n">
+      <c r="E6" s="127" t="n">
         <f aca="false">IF(ISNUMBER(D6),D6*C6,"-")</f>
         <v>132000</v>
       </c>
-      <c r="F6" s="125" t="s">
-        <v>519</v>
-      </c>
-      <c r="G6" s="125" t="s">
-        <v>520</v>
-      </c>
-      <c r="H6" s="122" t="s">
-        <v>521</v>
+      <c r="F6" s="128" t="s">
+        <v>574</v>
+      </c>
+      <c r="G6" s="128" t="s">
+        <v>575</v>
+      </c>
+      <c r="H6" s="125" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>523</v>
-      </c>
-      <c r="C7" s="126" t="n">
+        <v>578</v>
+      </c>
+      <c r="C7" s="129" t="n">
         <v>1750</v>
       </c>
       <c r="D7" s="64" t="n">
@@ -5742,71 +6479,71 @@
         <f aca="false">IF(ISNUMBER(D7),D7*C7,"-")</f>
         <v>48002.5</v>
       </c>
-      <c r="F7" s="127" t="s">
-        <v>520</v>
-      </c>
-      <c r="G7" s="128" t="s">
+      <c r="F7" s="130" t="s">
+        <v>575</v>
+      </c>
+      <c r="G7" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>524</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="C8" s="126" t="n">
+        <v>581</v>
+      </c>
+      <c r="C8" s="129" t="n">
         <v>3035</v>
       </c>
-      <c r="D8" s="129" t="s">
-        <v>527</v>
+      <c r="D8" s="132" t="s">
+        <v>582</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="F8" s="127" t="s">
-        <v>520</v>
-      </c>
-      <c r="G8" s="128" t="s">
+      <c r="F8" s="130" t="s">
+        <v>575</v>
+      </c>
+      <c r="G8" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>528</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="C9" s="126" t="s">
+        <v>585</v>
+      </c>
+      <c r="C9" s="129" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="129" t="s">
-        <v>527</v>
+      <c r="D9" s="132" t="s">
+        <v>582</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="F9" s="127" t="s">
-        <v>520</v>
-      </c>
-      <c r="G9" s="127" t="s">
-        <v>520</v>
+      <c r="F9" s="130" t="s">
+        <v>575</v>
+      </c>
+      <c r="G9" s="130" t="s">
+        <v>575</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>531</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>532</v>
+        <v>587</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -5818,10 +6555,10 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>513</v>
+        <v>568</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>101</v>
@@ -5830,26 +6567,26 @@
         <v>316</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>515</v>
+        <v>570</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>533</v>
+        <v>588</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="129" t="s">
         <v>337</v>
       </c>
       <c r="D13" s="64" t="n">
@@ -5859,24 +6596,24 @@
         <f aca="false">D13*Assumptions!$B$7</f>
         <v>105600</v>
       </c>
-      <c r="F13" s="128" t="s">
+      <c r="F13" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G13" s="128" t="s">
+      <c r="G13" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>534</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>535</v>
+        <v>590</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C14" s="126" t="s">
+        <v>591</v>
+      </c>
+      <c r="C14" s="129" t="s">
         <v>337</v>
       </c>
       <c r="D14" s="64" t="n">
@@ -5886,24 +6623,24 @@
         <f aca="false">D14*Assumptions!$B$7</f>
         <v>92400</v>
       </c>
-      <c r="F14" s="128" t="s">
+      <c r="F14" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G14" s="128" t="s">
+      <c r="G14" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>537</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>538</v>
+        <v>593</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C15" s="126" t="s">
+        <v>591</v>
+      </c>
+      <c r="C15" s="129" t="s">
         <v>337</v>
       </c>
       <c r="D15" s="64" t="n">
@@ -5913,24 +6650,24 @@
         <f aca="false">D15*Assumptions!$B$7</f>
         <v>88000</v>
       </c>
-      <c r="F15" s="128" t="s">
+      <c r="F15" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G15" s="128" t="s">
+      <c r="G15" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>537</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>539</v>
+        <v>594</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C16" s="126" t="s">
+        <v>591</v>
+      </c>
+      <c r="C16" s="129" t="s">
         <v>337</v>
       </c>
       <c r="D16" s="64" t="n">
@@ -5940,24 +6677,24 @@
         <f aca="false">D16*Assumptions!$B$7</f>
         <v>88000</v>
       </c>
-      <c r="F16" s="128" t="s">
+      <c r="F16" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G16" s="128" t="s">
+      <c r="G16" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>540</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>541</v>
+        <v>596</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C17" s="126" t="s">
+        <v>591</v>
+      </c>
+      <c r="C17" s="129" t="s">
         <v>337</v>
       </c>
       <c r="D17" s="64" t="n">
@@ -5967,24 +6704,24 @@
         <f aca="false">D17*Assumptions!$B$7</f>
         <v>57200</v>
       </c>
-      <c r="F17" s="128" t="s">
+      <c r="F17" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G17" s="128" t="s">
+      <c r="G17" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>542</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="C18" s="126" t="n">
+        <v>599</v>
+      </c>
+      <c r="C18" s="129" t="n">
         <v>40000</v>
       </c>
       <c r="D18" s="64" t="n">
@@ -5994,19 +6731,19 @@
         <f aca="false">D18*Assumptions!$B$7</f>
         <v>50600</v>
       </c>
-      <c r="F18" s="128" t="s">
+      <c r="F18" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="G18" s="128" t="s">
+      <c r="G18" s="131" t="s">
         <v>337</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>545</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>546</v>
+        <v>601</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -6018,16 +6755,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="43" t="s">
-        <v>547</v>
+        <v>602</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>548</v>
-      </c>
-      <c r="C21" s="130" t="n">
+        <v>603</v>
+      </c>
+      <c r="C21" s="133" t="n">
         <f aca="false">Assumptions!$B$7</f>
         <v>4400</v>
       </c>
-      <c r="D21" s="111" t="n">
+      <c r="D21" s="114" t="n">
         <f aca="false">Assumptions!$B$31</f>
         <v>22</v>
       </c>
@@ -6035,19 +6772,19 @@
         <f aca="false">Assumptions!$B$31*Assumptions!$B$7</f>
         <v>96800</v>
       </c>
-      <c r="F21" s="131" t="s">
-        <v>519</v>
-      </c>
-      <c r="G21" s="131" t="s">
-        <v>520</v>
+      <c r="F21" s="134" t="s">
+        <v>574</v>
+      </c>
+      <c r="G21" s="134" t="s">
+        <v>575</v>
       </c>
       <c r="H21" s="47" t="s">
-        <v>549</v>
+        <v>604</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>550</v>
+        <v>605</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -6071,29 +6808,29 @@
         <v>316</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>551</v>
+        <v>606</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>552</v>
+        <v>607</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>553</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>554</v>
+        <v>609</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="C25" s="126" t="n">
+        <v>610</v>
+      </c>
+      <c r="C25" s="129" t="n">
         <v>510</v>
       </c>
-      <c r="D25" s="132" t="n">
+      <c r="D25" s="135" t="n">
         <f aca="false">E25/C25</f>
         <v>303.921568627451</v>
       </c>
@@ -6101,26 +6838,26 @@
         <v>155000</v>
       </c>
       <c r="F25" s="109" t="s">
-        <v>556</v>
-      </c>
-      <c r="G25" s="133" t="s">
-        <v>557</v>
+        <v>611</v>
+      </c>
+      <c r="G25" s="136" t="s">
+        <v>612</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>558</v>
+        <v>613</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>559</v>
+        <v>614</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>560</v>
-      </c>
-      <c r="C26" s="126" t="n">
+        <v>615</v>
+      </c>
+      <c r="C26" s="129" t="n">
         <v>5585</v>
       </c>
-      <c r="D26" s="134" t="n">
+      <c r="D26" s="137" t="n">
         <f aca="false">E26/C26</f>
         <v>58.1915846016115</v>
       </c>
@@ -6128,26 +6865,26 @@
         <v>325000</v>
       </c>
       <c r="F26" s="109" t="s">
-        <v>556</v>
-      </c>
-      <c r="G26" s="133" t="s">
-        <v>557</v>
+        <v>611</v>
+      </c>
+      <c r="G26" s="136" t="s">
+        <v>612</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>561</v>
+        <v>616</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>562</v>
+        <v>617</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="C27" s="126" t="n">
+        <v>618</v>
+      </c>
+      <c r="C27" s="129" t="n">
         <v>3321</v>
       </c>
-      <c r="D27" s="134" t="n">
+      <c r="D27" s="137" t="n">
         <f aca="false">E27/C27</f>
         <v>47.4733514001807</v>
       </c>
@@ -6155,26 +6892,26 @@
         <v>157659</v>
       </c>
       <c r="F27" s="109" t="s">
-        <v>556</v>
-      </c>
-      <c r="G27" s="133" t="s">
-        <v>557</v>
+        <v>611</v>
+      </c>
+      <c r="G27" s="136" t="s">
+        <v>612</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>564</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>565</v>
+        <v>620</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="C28" s="126" t="n">
+        <v>621</v>
+      </c>
+      <c r="C28" s="129" t="n">
         <v>1373</v>
       </c>
-      <c r="D28" s="134" t="n">
+      <c r="D28" s="137" t="n">
         <f aca="false">E28/C28</f>
         <v>39.3299344501093</v>
       </c>
@@ -6182,26 +6919,26 @@
         <v>54000</v>
       </c>
       <c r="F28" s="109" t="s">
-        <v>567</v>
-      </c>
-      <c r="G28" s="133" t="s">
-        <v>568</v>
+        <v>622</v>
+      </c>
+      <c r="G28" s="136" t="s">
+        <v>623</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>569</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="24" t="s">
-        <v>570</v>
+        <v>625</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="C29" s="126" t="n">
+        <v>626</v>
+      </c>
+      <c r="C29" s="129" t="n">
         <v>14870</v>
       </c>
-      <c r="D29" s="134" t="n">
+      <c r="D29" s="137" t="n">
         <f aca="false">E29/C29</f>
         <v>31.1918628110289</v>
       </c>
@@ -6209,53 +6946,53 @@
         <v>463823</v>
       </c>
       <c r="F29" s="109" t="s">
-        <v>572</v>
-      </c>
-      <c r="G29" s="133" t="s">
-        <v>557</v>
+        <v>627</v>
+      </c>
+      <c r="G29" s="136" t="s">
+        <v>612</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>573</v>
+        <v>628</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="88" t="s">
-        <v>574</v>
+        <v>629</v>
       </c>
       <c r="B30" s="93" t="s">
-        <v>575</v>
-      </c>
-      <c r="C30" s="130" t="n">
+        <v>630</v>
+      </c>
+      <c r="C30" s="133" t="n">
         <v>3300</v>
       </c>
-      <c r="D30" s="111" t="n">
+      <c r="D30" s="114" t="n">
         <f aca="false">E30/C30</f>
         <v>27.96</v>
       </c>
       <c r="E30" s="91" t="n">
         <v>92268</v>
       </c>
-      <c r="F30" s="135" t="s">
-        <v>567</v>
+      <c r="F30" s="138" t="s">
+        <v>622</v>
       </c>
       <c r="G30" s="92" t="s">
-        <v>576</v>
+        <v>631</v>
       </c>
       <c r="H30" s="93" t="s">
-        <v>577</v>
+        <v>632</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="24" t="s">
-        <v>578</v>
+        <v>633</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="C31" s="126" t="n">
+        <v>634</v>
+      </c>
+      <c r="C31" s="129" t="n">
         <v>19054</v>
       </c>
-      <c r="D31" s="134" t="n">
+      <c r="D31" s="137" t="n">
         <f aca="false">E31/C31</f>
         <v>12.9605332213708</v>
       </c>
@@ -6263,18 +7000,18 @@
         <v>246950</v>
       </c>
       <c r="F31" s="109" t="s">
-        <v>580</v>
-      </c>
-      <c r="G31" s="133" t="s">
-        <v>557</v>
+        <v>635</v>
+      </c>
+      <c r="G31" s="136" t="s">
+        <v>612</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>581</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>582</v>
+        <v>637</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -6286,25 +7023,25 @@
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>584</v>
+        <v>639</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>585</v>
+        <v>640</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6" t="s">
-        <v>586</v>
+        <v>641</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>587</v>
+        <v>642</v>
       </c>
       <c r="B35" s="37" t="n">
         <v>27.96</v>
@@ -6313,12 +7050,12 @@
         <v>27.43</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>588</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="20" t="s">
-        <v>589</v>
+        <v>644</v>
       </c>
       <c r="B36" s="41" t="n">
         <v>0.9</v>
@@ -6327,12 +7064,12 @@
         <v>0.8</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>590</v>
+        <v>645</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="s">
-        <v>591</v>
+        <v>646</v>
       </c>
       <c r="B37" s="41" t="n">
         <v>0.9</v>
@@ -6341,12 +7078,12 @@
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>592</v>
+        <v>647</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="s">
-        <v>593</v>
+        <v>648</v>
       </c>
       <c r="B38" s="41" t="n">
         <v>0.95</v>
@@ -6355,18 +7092,18 @@
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>594</v>
+        <v>649</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="43" t="s">
-        <v>595</v>
-      </c>
-      <c r="B39" s="111" t="n">
+        <v>650</v>
+      </c>
+      <c r="B39" s="114" t="n">
         <f aca="false">B35*B36*B37*B38</f>
         <v>21.51522</v>
       </c>
-      <c r="C39" s="111" t="n">
+      <c r="C39" s="114" t="n">
         <f aca="false">C35*C36*C37*C38</f>
         <v>21.944</v>
       </c>
@@ -6375,12 +7112,12 @@
       <c r="F39" s="45"/>
       <c r="G39" s="45"/>
       <c r="H39" s="47" t="s">
-        <v>596</v>
+        <v>651</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>597</v>
+        <v>652</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -6392,10 +7129,10 @@
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="105" t="s">
-        <v>598</v>
+        <v>653</v>
       </c>
       <c r="B42" s="106" t="s">
-        <v>599</v>
+        <v>654</v>
       </c>
       <c r="C42" s="106"/>
       <c r="D42" s="106"/>
@@ -6406,10 +7143,10 @@
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="105" t="s">
-        <v>600</v>
+        <v>655</v>
       </c>
       <c r="B43" s="106" t="s">
-        <v>601</v>
+        <v>656</v>
       </c>
       <c r="C43" s="106"/>
       <c r="D43" s="106"/>
@@ -6420,10 +7157,10 @@
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="105" t="s">
-        <v>602</v>
+        <v>657</v>
       </c>
       <c r="B44" s="106" t="s">
-        <v>603</v>
+        <v>658</v>
       </c>
       <c r="C44" s="106"/>
       <c r="D44" s="106"/>
@@ -6434,10 +7171,10 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="105" t="s">
-        <v>604</v>
+        <v>659</v>
       </c>
       <c r="B45" s="106" t="s">
-        <v>605</v>
+        <v>660</v>
       </c>
       <c r="C45" s="106"/>
       <c r="D45" s="106"/>
@@ -6448,10 +7185,10 @@
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="105" t="s">
-        <v>606</v>
+        <v>661</v>
       </c>
       <c r="B46" s="106" t="s">
-        <v>607</v>
+        <v>662</v>
       </c>
       <c r="C46" s="106"/>
       <c r="D46" s="106"/>
@@ -6462,10 +7199,10 @@
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="105" t="s">
-        <v>608</v>
+        <v>663</v>
       </c>
       <c r="B47" s="106" t="s">
-        <v>609</v>
+        <v>664</v>
       </c>
       <c r="C47" s="106"/>
       <c r="D47" s="106"/>
@@ -6476,7 +7213,7 @@
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="48" t="s">
-        <v>610</v>
+        <v>665</v>
       </c>
       <c r="B49" s="48"/>
       <c r="C49" s="48"/>
@@ -6514,7 +7251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -6531,7 +7268,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>611</v>
+        <v>666</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6540,7 +7277,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>612</v>
+        <v>667</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6549,24 +7286,24 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>613</v>
+        <v>668</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>614</v>
+        <v>669</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>615</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>616</v>
+        <v>671</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>337</v>
@@ -6575,15 +7312,15 @@
         <v>0.068</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>617</v>
+        <v>672</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>618</v>
+        <v>673</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>619</v>
+        <v>674</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>337</v>
@@ -6592,15 +7329,15 @@
         <v>0.074</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>620</v>
+        <v>675</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>621</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>622</v>
+        <v>677</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>3100000</v>
@@ -6609,32 +7346,32 @@
         <v>0.0825</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>623</v>
+        <v>678</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>621</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="121" t="s">
-        <v>624</v>
-      </c>
-      <c r="B8" s="124" t="n">
+      <c r="A8" s="124" t="s">
+        <v>679</v>
+      </c>
+      <c r="B8" s="127" t="n">
         <v>1600000</v>
       </c>
-      <c r="C8" s="136" t="n">
+      <c r="C8" s="139" t="n">
         <v>0.0825</v>
       </c>
-      <c r="D8" s="122" t="s">
-        <v>625</v>
-      </c>
-      <c r="E8" s="137" t="s">
-        <v>626</v>
+      <c r="D8" s="125" t="s">
+        <v>680</v>
+      </c>
+      <c r="E8" s="140" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>627</v>
+        <v>682</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>1025000</v>
@@ -6643,15 +7380,15 @@
         <v>0.0887</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="E9" s="138" t="s">
-        <v>629</v>
+        <v>683</v>
+      </c>
+      <c r="E9" s="141" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>337</v>
@@ -6660,15 +7397,15 @@
         <v>0.0925</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>621</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>632</v>
+        <v>687</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>337</v>
@@ -6677,15 +7414,15 @@
         <v>0.0935</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>633</v>
+        <v>688</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>621</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>634</v>
+        <v>689</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>337</v>
@@ -6694,15 +7431,15 @@
         <v>0.0875</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>635</v>
+        <v>690</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>618</v>
+        <v>673</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="s">
-        <v>636</v>
+        <v>691</v>
       </c>
       <c r="B13" s="52" t="n">
         <f aca="false">Assumptions!$B$15</f>
@@ -6713,15 +7450,15 @@
         <v>0.12</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>637</v>
-      </c>
-      <c r="E13" s="139" t="s">
-        <v>638</v>
+        <v>692</v>
+      </c>
+      <c r="E13" s="142" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>639</v>
+        <v>694</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -6730,16 +7467,16 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>642</v>
+        <v>697</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>583</v>
+        <v>638</v>
       </c>
       <c r="E16" s="6"/>
     </row>
@@ -6748,43 +7485,43 @@
         <v>121</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>644</v>
+        <v>699</v>
       </c>
       <c r="D17" s="97" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="E17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>647</v>
+        <v>702</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="D18" s="97" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>650</v>
+        <v>705</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>652</v>
+        <v>707</v>
       </c>
       <c r="D19" s="97" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="E19" s="10"/>
     </row>
@@ -6793,82 +7530,82 @@
         <v>131</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="D20" s="97" t="s">
-        <v>655</v>
+        <v>710</v>
       </c>
       <c r="E20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>658</v>
+        <v>713</v>
       </c>
       <c r="D21" s="97" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
       <c r="E21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>660</v>
+        <v>715</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>661</v>
+        <v>716</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>662</v>
+        <v>717</v>
       </c>
       <c r="D22" s="96" t="s">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="E22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>661</v>
+        <v>716</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>665</v>
+        <v>720</v>
       </c>
       <c r="D23" s="96" t="s">
-        <v>666</v>
+        <v>721</v>
       </c>
       <c r="E23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="43" t="s">
-        <v>667</v>
-      </c>
-      <c r="B24" s="140" t="s">
-        <v>668</v>
-      </c>
-      <c r="C24" s="140" t="s">
-        <v>669</v>
+        <v>722</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>723</v>
+      </c>
+      <c r="C24" s="143" t="s">
+        <v>724</v>
       </c>
       <c r="D24" s="62" t="n">
         <f aca="false">Assumptions!$B$22/Assumptions!$B$15</f>
         <v>0.12</v>
       </c>
-      <c r="E24" s="141" t="s">
-        <v>670</v>
+      <c r="E24" s="144" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="B26" s="48"/>
       <c r="C26" s="48"/>
@@ -6892,7 +7629,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -6907,194 +7644,194 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>672</v>
+        <v>727</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>674</v>
+        <v>729</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>675</v>
+        <v>730</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>676</v>
+        <v>731</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>677</v>
+        <v>732</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>678</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>679</v>
+        <v>734</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>680</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>681</v>
+        <v>736</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>682</v>
+        <v>737</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>683</v>
+        <v>738</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>684</v>
+        <v>739</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>685</v>
+        <v>740</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>686</v>
+        <v>741</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>687</v>
+        <v>742</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>688</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>689</v>
+        <v>744</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>690</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="20" t="s">
-        <v>691</v>
+        <v>746</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>692</v>
+        <v>747</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>693</v>
+        <v>748</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="142" t="s">
-        <v>694</v>
+      <c r="A16" s="145" t="s">
+        <v>749</v>
       </c>
       <c r="B16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="143" t="s">
-        <v>695</v>
-      </c>
-      <c r="B17" s="143"/>
+      <c r="A17" s="146" t="s">
+        <v>750</v>
+      </c>
+      <c r="B17" s="146"/>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="143" t="s">
-        <v>696</v>
-      </c>
-      <c r="B18" s="143"/>
+      <c r="A18" s="146" t="s">
+        <v>751</v>
+      </c>
+      <c r="B18" s="146"/>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="143" t="s">
-        <v>697</v>
-      </c>
-      <c r="B19" s="143"/>
+      <c r="A19" s="146" t="s">
+        <v>752</v>
+      </c>
+      <c r="B19" s="146"/>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="143" t="s">
-        <v>698</v>
-      </c>
-      <c r="B20" s="143"/>
+      <c r="A20" s="146" t="s">
+        <v>753</v>
+      </c>
+      <c r="B20" s="146"/>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="143" t="s">
-        <v>699</v>
-      </c>
-      <c r="B21" s="143"/>
+      <c r="A21" s="146" t="s">
+        <v>754</v>
+      </c>
+      <c r="B21" s="146"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="143" t="s">
-        <v>700</v>
-      </c>
-      <c r="B22" s="143"/>
+      <c r="A22" s="146" t="s">
+        <v>755</v>
+      </c>
+      <c r="B22" s="146"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="142" t="s">
-        <v>701</v>
+      <c r="A24" s="145" t="s">
+        <v>756</v>
       </c>
       <c r="B24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="143" t="s">
-        <v>702</v>
-      </c>
-      <c r="B25" s="143"/>
+      <c r="A25" s="146" t="s">
+        <v>757</v>
+      </c>
+      <c r="B25" s="146"/>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="143" t="s">
-        <v>703</v>
-      </c>
-      <c r="B26" s="143"/>
+      <c r="A26" s="146" t="s">
+        <v>758</v>
+      </c>
+      <c r="B26" s="146"/>
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="143" t="s">
-        <v>704</v>
-      </c>
-      <c r="B27" s="143"/>
+      <c r="A27" s="146" t="s">
+        <v>759</v>
+      </c>
+      <c r="B27" s="146"/>
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="143" t="s">
-        <v>705</v>
-      </c>
-      <c r="B28" s="143"/>
+      <c r="A28" s="146" t="s">
+        <v>760</v>
+      </c>
+      <c r="B28" s="146"/>
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="143" t="s">
-        <v>706</v>
-      </c>
-      <c r="B29" s="143"/>
+      <c r="A29" s="146" t="s">
+        <v>761</v>
+      </c>
+      <c r="B29" s="146"/>
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="143" t="s">
-        <v>707</v>
-      </c>
-      <c r="B30" s="143"/>
+      <c r="A30" s="146" t="s">
+        <v>762</v>
+      </c>
+      <c r="B30" s="146"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="143" t="s">
-        <v>708</v>
-      </c>
-      <c r="B31" s="143"/>
+      <c r="A31" s="146" t="s">
+        <v>763</v>
+      </c>
+      <c r="B31" s="146"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -11824,13 +12561,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="12" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="2" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11845,6 +12580,9 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -11858,6 +12596,9 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -11871,45 +12612,16 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="L4" s="51" t="n">
-        <f aca="false">-B18</f>
-        <v>-495000</v>
-      </c>
-      <c r="M4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="N4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="O4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="P4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="Q4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="R4" s="51" t="n">
-        <f aca="false">C18</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="S4" s="51" t="n">
-        <f aca="false">C18*0.5+E18</f>
-        <v>643328.111643992</v>
-      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B5" s="38" t="n">
-        <v>0.55</v>
+      <c r="B5" s="37" t="n">
+        <v>24</v>
       </c>
       <c r="C5" s="53" t="s">
         <v>429</v>
@@ -11920,45 +12632,16 @@
       <c r="G5" s="53"/>
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
-      <c r="L5" s="51" t="n">
-        <f aca="false">-B19</f>
-        <v>-562500</v>
-      </c>
-      <c r="M5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="N5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="O5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="P5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="Q5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="R5" s="51" t="n">
-        <f aca="false">C19</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="S5" s="51" t="n">
-        <f aca="false">C19*0.5+E19</f>
-        <v>563122.791792153</v>
-      </c>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
         <v>430</v>
       </c>
       <c r="B6" s="38" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="C6" s="53" t="s">
         <v>431</v>
@@ -11969,45 +12652,16 @@
       <c r="G6" s="53"/>
       <c r="H6" s="53"/>
       <c r="I6" s="53"/>
-      <c r="L6" s="51" t="n">
-        <f aca="false">-B20</f>
-        <v>-720000</v>
-      </c>
-      <c r="M6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="N6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="O6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="P6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="Q6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="R6" s="51" t="n">
-        <f aca="false">C20</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="S6" s="51" t="n">
-        <f aca="false">C20*0.5+E20</f>
-        <v>375977.045471196</v>
-      </c>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B7" s="103" t="n">
-        <v>25</v>
+      <c r="B7" s="34" t="n">
+        <v>264000</v>
       </c>
       <c r="C7" s="53" t="s">
         <v>433</v>
@@ -12018,13 +12672,16 @@
       <c r="G7" s="53"/>
       <c r="H7" s="53"/>
       <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B8" s="36" t="n">
-        <v>6.5</v>
+      <c r="B8" s="34" t="n">
+        <v>52800</v>
       </c>
       <c r="C8" s="53" t="s">
         <v>435</v>
@@ -12035,338 +12692,618 @@
       <c r="G8" s="53"/>
       <c r="H8" s="53"/>
       <c r="I8" s="53"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="B9" s="38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C9" s="53" t="s">
         <v>437</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="B10" s="38" t="n">
+        <v>0.085</v>
+      </c>
+      <c r="C10" s="53" t="s">
         <v>439</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="B11" s="38" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C11" s="53" t="s">
         <v>441</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>444</v>
-      </c>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="53"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" s="25" t="n">
-        <f aca="false">Assumptions!$B$15*$B$5</f>
-        <v>605000</v>
-      </c>
-      <c r="C12" s="25" t="n">
-        <f aca="false">Assumptions!$B$15-B12</f>
-        <v>495000</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <f aca="false">-PMT($B$6/12,$B$7*12,B12)*12</f>
-        <v>65971.6741262084</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>132000</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <f aca="false">E12/D12</f>
-        <v>2.00085872836082</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <f aca="false">E12-D12</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <f aca="false">G12/C12</f>
-        <v>0.133390557320791</v>
-      </c>
-      <c r="I12" s="11" t="str">
-        <f aca="false">IF(F12&gt;=1.5,"Comfortably financeable",IF(F12&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
-        <v>Comfortably financeable</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="25" t="n">
-        <f aca="false">Assumptions!$B$16*$B$5</f>
-        <v>687500</v>
-      </c>
-      <c r="C13" s="25" t="n">
-        <f aca="false">Assumptions!$B$16-B13</f>
-        <v>562500</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <f aca="false">-PMT($B$6/12,$B$7*12,B13)*12</f>
-        <v>74967.811507055</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>132000</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <f aca="false">E13/D13</f>
-        <v>1.76075568095752</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <f aca="false">E13-D13</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <f aca="false">G13/C13</f>
-        <v>0.101390557320791</v>
-      </c>
-      <c r="I13" s="11" t="str">
-        <f aca="false">IF(F13&gt;=1.5,"Comfortably financeable",IF(F13&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
-        <v>Comfortably financeable</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="25" t="n">
-        <f aca="false">Assumptions!$B$14*$B$5</f>
-        <v>880000</v>
-      </c>
-      <c r="C14" s="25" t="n">
-        <f aca="false">Assumptions!$B$14-B14</f>
-        <v>720000</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <f aca="false">-PMT($B$6/12,$B$7*12,B14)*12</f>
-        <v>95958.7987290304</v>
-      </c>
-      <c r="E14" s="42" t="n">
-        <f aca="false">Assumptions!$B$22</f>
-        <v>132000</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <f aca="false">E14/D14</f>
-        <v>1.37559037574807</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <f aca="false">E14-D14</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <f aca="false">G14/C14</f>
-        <v>0.0500572239874578</v>
-      </c>
-      <c r="I14" s="11" t="str">
-        <f aca="false">IF(F14&gt;=1.5,"Comfortably financeable",IF(F14&gt;=1.25,"Financeable, tight","Lender would decline"))</f>
-        <v>Financeable, tight</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" s="37" t="n">
+        <v>18</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="C15" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="L15" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="B16" s="27" t="n">
+        <f aca="false">-Assumptions!$B$15</f>
+        <v>-1100000</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>132000</v>
+      </c>
+      <c r="D16" s="25" t="n">
+        <f aca="false">Assumptions!$B$22+-Assumptions!$B$46</f>
+        <v>-18000</v>
+      </c>
+      <c r="E16" s="111" t="n">
+        <f aca="false">Assumptions!$B$22+('Land Upside'!$C$15)</f>
+        <v>232000</v>
+      </c>
+      <c r="F16" s="111" t="n">
+        <f aca="false">Assumptions!$B$22+('Land Upside'!$C$15)</f>
+        <v>232000</v>
+      </c>
+      <c r="G16" s="111" t="n">
+        <f aca="false">Assumptions!$B$22+('Land Upside'!$C$15)</f>
+        <v>232000</v>
+      </c>
+      <c r="H16" s="111" t="n">
+        <f aca="false">Assumptions!$B$22+('Land Upside'!$C$15)</f>
+        <v>232000</v>
+      </c>
+      <c r="I16" s="111" t="n">
+        <f aca="false">Assumptions!$B$22*0.5-(Assumptions!$B$36+Assumptions!$B$37+Assumptions!$B$38)*0.5+('Land Upside'!$C$15)</f>
+        <v>135299</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <f aca="false">('Land Upside'!$C$15)+-$B$7-$B$8-(Assumptions!$B$36+Assumptions!$B$37+Assumptions!$B$38)*0.5</f>
+        <v>-247501</v>
+      </c>
+      <c r="K16" s="111" t="n">
+        <f aca="false">('Land Upside'!$C$15)+$B$5*Assumptions!$B$7*(1+$B$6)^(9-9)</f>
+        <v>205600</v>
+      </c>
+      <c r="L16" s="111" t="n">
+        <f aca="false">('Land Upside'!$C$15)+$B$5*Assumptions!$B$7*(1+$B$6)^(10-9)</f>
+        <v>208240</v>
+      </c>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="B17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <f aca="false">($B$5*Assumptions!$B$7*(1+$B$6)^2+('Land Upside'!$C$15))/$B$9</f>
+        <v>2636825</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B18" s="25" t="n">
-        <f aca="false">C12</f>
-        <v>495000</v>
-      </c>
-      <c r="C18" s="25" t="n">
-        <f aca="false">G12</f>
-        <v>66028.3258737916</v>
-      </c>
-      <c r="D18" s="25" t="n">
-        <f aca="false">B12*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B12))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
-        <v>555186.508517046</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <f aca="false">'Reversion Scenarios'!$G$11-D18</f>
-        <v>610313.948707096</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <f aca="false">IRR(L4:S4)</f>
-        <v>0.148484517194147</v>
-      </c>
-      <c r="G18" s="65" t="n">
-        <f aca="false">Returns!$D$31</f>
-        <v>0.119954981443023</v>
-      </c>
-      <c r="H18" s="65" t="n">
-        <f aca="false">F18-G18</f>
-        <v>0.0285295357511241</v>
-      </c>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B19" s="25" t="n">
-        <f aca="false">C13</f>
-        <v>562500</v>
-      </c>
-      <c r="C19" s="25" t="n">
-        <f aca="false">G13</f>
-        <v>57032.188492945</v>
-      </c>
-      <c r="D19" s="25" t="n">
-        <f aca="false">B13*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B13))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
-        <v>630893.759678461</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <f aca="false">'Reversion Scenarios'!$G$11-D19</f>
-        <v>534606.69754568</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <f aca="false">IRR(L5:S5)</f>
-        <v>0.09050766214664</v>
-      </c>
-      <c r="G19" s="65" t="n">
-        <f aca="false">Returns!$D$34</f>
-        <v>0.0926183792510331</v>
-      </c>
-      <c r="H19" s="65" t="n">
-        <f aca="false">F19-G19</f>
-        <v>-0.00211071710439302</v>
-      </c>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="25" t="n">
-        <f aca="false">C14</f>
-        <v>720000</v>
-      </c>
-      <c r="C20" s="25" t="n">
-        <f aca="false">G14</f>
-        <v>36041.2012709696</v>
-      </c>
-      <c r="D20" s="25" t="n">
-        <f aca="false">B14*(1+$B$6/12)^($B$8*12)-(-PMT($B$6/12,$B$7*12,B14))*((1+$B$6/12)^($B$8*12)-1)/($B$6/12)</f>
-        <v>807544.01238843</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <f aca="false">'Reversion Scenarios'!$G$11-D20</f>
-        <v>357956.444835711</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <f aca="false">IRR(L6:S6)</f>
-        <v>-0.0332012262877994</v>
-      </c>
-      <c r="G20" s="65" t="n">
-        <f aca="false">Returns!$D$37</f>
-        <v>0.0432884758639595</v>
-      </c>
-      <c r="H20" s="65" t="n">
-        <f aca="false">F20-G20</f>
-        <v>-0.0764897021517589</v>
-      </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="48" t="s">
+      <c r="B18" s="52" t="n">
+        <f aca="false">SUM(B16:B17)</f>
+        <v>-1100000</v>
+      </c>
+      <c r="C18" s="52" t="n">
+        <f aca="false">SUM(C16:C17)</f>
+        <v>132000</v>
+      </c>
+      <c r="D18" s="52" t="n">
+        <f aca="false">SUM(D16:D17)</f>
+        <v>-18000</v>
+      </c>
+      <c r="E18" s="52" t="n">
+        <f aca="false">SUM(E16:E17)</f>
+        <v>232000</v>
+      </c>
+      <c r="F18" s="52" t="n">
+        <f aca="false">SUM(F16:F17)</f>
+        <v>232000</v>
+      </c>
+      <c r="G18" s="52" t="n">
+        <f aca="false">SUM(G16:G17)</f>
+        <v>232000</v>
+      </c>
+      <c r="H18" s="52" t="n">
+        <f aca="false">SUM(H16:H17)</f>
+        <v>232000</v>
+      </c>
+      <c r="I18" s="52" t="n">
+        <f aca="false">SUM(I16:I17)</f>
+        <v>135299</v>
+      </c>
+      <c r="J18" s="52" t="n">
+        <f aca="false">SUM(J16:J17)</f>
+        <v>-247501</v>
+      </c>
+      <c r="K18" s="52" t="n">
+        <f aca="false">SUM(K16:K17)</f>
+        <v>205600</v>
+      </c>
+      <c r="L18" s="52" t="n">
+        <f aca="false">SUM(L16:L17)</f>
+        <v>2845065</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B22" s="38" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="53"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="48"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
+      <c r="A23" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B23" s="38" t="n">
+        <v>0.0874</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>460</v>
+      </c>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
+        <v>461</v>
+      </c>
+      <c r="B24" s="62" t="n">
+        <f aca="false">IRR(B18:L18)</f>
+        <v>0.182139708604639</v>
+      </c>
+      <c r="C24" s="112" t="s">
+        <v>462</v>
+      </c>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="B28" s="25" t="n">
+        <f aca="false">Assumptions!$B$22</f>
+        <v>132000</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <f aca="false">Assumptions!$B$15</f>
+        <v>1100000</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B29" s="25" t="n">
+        <f aca="false">Assumptions!$B$22+('Land Upside'!$C$15)</f>
+        <v>232000</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <f aca="false">B29/0.0925</f>
+        <v>2508108.10810811</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="11" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
+        <v>471</v>
+      </c>
+      <c r="B30" s="25" t="n">
+        <f aca="false">$B$5*Assumptions!$B$7+('Land Upside'!$C$15)</f>
+        <v>205600</v>
+      </c>
+      <c r="C30" s="27" t="n">
+        <f aca="false">B30/0.0825</f>
+        <v>2492121.21212121</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="11" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="B31" s="25" t="n">
+        <f aca="false">$B$5*Assumptions!$B$7+('Land Upside'!$C$15)</f>
+        <v>205600</v>
+      </c>
+      <c r="C31" s="27" t="n">
+        <f aca="false">B31/0.0775</f>
+        <v>2652903.22580645</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="11" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="113" t="n">
+        <f aca="false">-(Assumptions!$B$46+$B$7+$B$8)</f>
+        <v>-466800</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="11" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="43" t="s">
+        <v>477</v>
+      </c>
+      <c r="B33" s="52" t="n">
+        <f aca="false">B31</f>
+        <v>205600</v>
+      </c>
+      <c r="C33" s="46" t="n">
+        <f aca="false">C31+C32</f>
+        <v>2186103.22580645</v>
+      </c>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="47" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <f aca="false">C33/Assumptions!$B$15-1</f>
+        <v>0.987366568914956</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="48" t="s">
+        <v>480</v>
+      </c>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="A22:I23"/>
+  <mergeCells count="18">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="C6:L6"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="C11:L11"/>
+    <mergeCell ref="C12:L12"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A36:L37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
